--- a/docs/REPAIR01_20260823/navarch/SILENT_DROP_FIX_REPORT.xlsx
+++ b/docs/REPAIR01_20260823/navarch/SILENT_DROP_FIX_REPORT.xlsx
@@ -149,7 +149,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">لقطةٌ واحدةٌ للقياساتِ الثلاثة: `0fcaa85b`</t>
+          <t xml:space="preserve">لقطةٌ واحدةٌ للقياساتِ الثلاثة: `261ad623`</t>
         </is>
       </c>
     </row>

--- a/docs/REPAIR01_20260823/navarch/SILENT_DROP_FIX_REPORT.xlsx
+++ b/docs/REPAIR01_20260823/navarch/SILENT_DROP_FIX_REPORT.xlsx
@@ -137,7 +137,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 من 69</t>
+          <t xml:space="preserve">56 من 69</t>
         </is>
       </c>
     </row>
@@ -149,7 +149,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">لقطةٌ واحدةٌ للقياساتِ الثلاثة: `261ad623`</t>
+          <t xml:space="preserve">لقطةٌ واحدةٌ للقياساتِ الثلاثة: `07e5284d`</t>
         </is>
       </c>
     </row>
@@ -260,7 +260,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -317,7 +317,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Damage/Incident Claim)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -438,7 +438,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Child of ش03)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Child of ش05)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Child of خ06)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Reference — Credit Control) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ① الجدول · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ② بطاقاتُ الإحصاء · ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">قائمٌ: ③ الفلاتر · ④ نموذجُ الإضافة · DataTable · عن الشاشة ⇐ **ينقص**: ② بطاقاتُ الإحصاء</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Instrument Register) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Interbank Transfers) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — FX Execution) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Guarantees/LCs) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Child of ب03 — Employee Documents) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Personnel Movements) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Training/Competence) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Benefits/Insurance) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Reference — Policy Register) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Regulatory Filings) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Conflict of Interest) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Reference — Related Parties) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Gifts &amp; Hospitality) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — CoC Acknowledgements) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Whistleblowing) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Investigations) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Breach Register) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — Corrective Actions) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Reference — Committees) · ⭐ أُضيف صندوقُ الفلترة</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Transaction — External Repair &amp; Warranty)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمٌ: ② بطاقاتُ الإحصاء · ③ الفلاتر · DataTable · عن الشاشة ⇐ **ينقص**: ④ نموذجُ الإضافة</t>
+          <t xml:space="preserve">مطابقٌ تامًّا لعقدِ نوعِه (Event — Daily Care &amp; Lubrication)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/docs/REPAIR01_20260823/navarch/SILENT_DROP_FIX_REPORT.xlsx
+++ b/docs/REPAIR01_20260823/navarch/SILENT_DROP_FIX_REPORT.xlsx
@@ -149,7 +149,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">لقطةٌ واحدةٌ للقياساتِ الثلاثة: `07e5284d`</t>
+          <t xml:space="preserve">لقطةٌ واحدةٌ للقياساتِ الثلاثة: `d0fca21d`</t>
         </is>
       </c>
     </row>
